--- a/source/rv32imacbfv_todo.xlsx
+++ b/source/rv32imacbfv_todo.xlsx
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">COUNTIF(Görevler!$H$2:$H$98,"Tamamlandı")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">COUNTIF(Görevler!$H$2:$H$98,"Yapılacak")</f>
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">IFERROR(B5/B4,0)</f>
-        <v>0.175257731958763</v>
+        <v>0.185567010309278</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1809,11 +1809,11 @@
       </c>
       <c r="C14" s="9" t="n">
         <f aca="false">COUNTIFS(Görevler!$B$2:$B$98,$A14,Görevler!$H$2:$H$98,"Tamamlandı")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">IFERROR(C14/B14,0)</f>
-        <v>0.615384615384615</v>
+        <v>0.692307692307692</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2843,7 +2843,7 @@
         <v>77</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>78</v>
